--- a/data/trans_dic/P1435_2011_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1435_2011_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,35</t>
+          <t>0,7; 3,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,73</t>
+          <t>2,59; 9,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,71</t>
+          <t>0,45; 1,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,59</t>
+          <t>1,43; 5,48</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,94</t>
+          <t>0,26; 2,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,27</t>
+          <t>1,37; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,41</t>
+          <t>3,04; 6,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,08</t>
+          <t>0,74; 2,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,14</t>
+          <t>1,75; 4,06</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -797,27 +797,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,47</t>
+          <t>0,38; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,34</t>
+          <t>1,84; 4,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,01</t>
+          <t>4,67; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,27</t>
+          <t>0,84; 2,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,93</t>
+          <t>2,77; 4,69</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,64</t>
+          <t>0,16; 1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,06</t>
+          <t>1,34; 3,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 8,37</t>
+          <t>4,06; 8,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,14</t>
+          <t>7,72; 11,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,75</t>
+          <t>2,37; 4,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,81</t>
+          <t>4,96; 7,05</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,97</t>
+          <t>0,24; 2,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,0</t>
+          <t>1,0; 2,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,44</t>
+          <t>5,39; 10,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 17,08</t>
+          <t>13,07; 17,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,74</t>
+          <t>2,96; 5,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,92; 9,48</t>
+          <t>7,35; 9,81</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1037,27 +1037,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,43</t>
+          <t>1,43; 4,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,33</t>
+          <t>1,67; 5,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,94; 76,88</t>
+          <t>9,93; 14,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,94</t>
+          <t>0,88; 3,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 62,93</t>
+          <t>6,28; 9,07</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,21</t>
+          <t>0,7; 3,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,5</t>
+          <t>0,25; 2,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,8</t>
+          <t>6,73; 10,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,81</t>
+          <t>0,21; 1,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,28</t>
+          <t>4,52; 7,13</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1197,27 +1197,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,26; 2,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,23</t>
+          <t>3,01; 4,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,49; 28,64</t>
+          <t>8,25; 9,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,32</t>
+          <t>1,64; 2,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,05; 18,81</t>
+          <t>4,94; 5,93</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>23206</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4780</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 22797</t>
+          <t>0; 24052</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3081; 14423</t>
+          <t>2994; 13419</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7250; 30473</t>
+          <t>9382; 35475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3909; 15145</t>
+          <t>3967; 15235</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11337; 39887</t>
+          <t>11001; 42202</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>27536</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6560</t>
+          <t>0; 6237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1508; 12444</t>
+          <t>1234; 12516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8806; 26083</t>
+          <t>8357; 23939</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10956; 32769</t>
+          <t>15244; 34534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10122; 27018</t>
+          <t>9622; 28262</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16116; 38743</t>
+          <t>17151; 39741</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>45743</t>
         </is>
       </c>
     </row>
@@ -1666,27 +1666,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2884; 13240</t>
+          <t>2336; 14186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12237; 30832</t>
+          <t>13065; 31467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25790; 43350</t>
+          <t>28957; 48687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12848; 31602</t>
+          <t>11753; 30884</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31676; 53097</t>
+          <t>34367; 58280</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68793</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84077</t>
+          <t>84529</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>993; 10100</t>
+          <t>984; 10013</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5583; 27120</t>
+          <t>9376; 25709</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25735; 51606</t>
+          <t>24995; 50177</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54610; 86493</t>
+          <t>56851; 82526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29348; 58497</t>
+          <t>29192; 57365</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47829; 108886</t>
+          <t>71160; 101234</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79946</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89790</t>
+          <t>103646</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1041; 8474</t>
+          <t>1038; 9062</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5026; 16834</t>
+          <t>6089; 18023</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22702; 46731</t>
+          <t>24117; 47607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68666; 92798</t>
+          <t>79051; 107210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24724; 50333</t>
+          <t>26004; 51758</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76316; 104666</t>
+          <t>89163; 119013</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251754</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>63813</t>
         </is>
       </c>
     </row>
@@ -2020,27 +2020,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5783; 16267</t>
+          <t>5824; 17114</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5912; 18883</t>
+          <t>5917; 17917</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66501; 467461</t>
+          <t>43571; 63435</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5893; 19532</t>
+          <t>5865; 20015</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67055; 613892</t>
+          <t>53054; 76622</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>44841</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5263</t>
+          <t>0; 6097</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2241; 9077</t>
+          <t>2160; 9486</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>994; 9724</t>
+          <t>985; 10983</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28620; 45993</t>
+          <t>31280; 50521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1090; 11545</t>
+          <t>1313; 11224</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32938; 51604</t>
+          <t>35003; 55272</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5833; 19341</t>
+          <t>5913; 19055</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>39830; 75382</t>
+          <t>44605; 76856</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105213; 150344</t>
+          <t>106935; 151587</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>310448; 1046860</t>
+          <t>307501; 364220</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>114320; 161872</t>
+          <t>114317; 162651</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>358827; 1338126</t>
+          <t>358755; 430079</t>
         </is>
       </c>
     </row>
